--- a/examples/demo_data/外审人员登记表.xlsx
+++ b/examples/demo_data/外审人员登记表.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中审会计师事务所</t>
+          <t>示例会计师事务所</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13759943324</t>
+          <t>13800000001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>华信评估公司</t>
+          <t>示例评估公司</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13859941188</t>
+          <t>13800000002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>方圆咨询</t>
+          <t>示例咨询公司</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中审会计师事务所</t>
+          <t>示例会计师事务所</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13677889900</t>
+          <t>13800000004</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>莱茵检测</t>
+          <t>示例检测公司</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13566778899</t>
+          <t>13800000005</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
